--- a/site/assets/files/grad-school-application-tracker.xlsx
+++ b/site/assets/files/grad-school-application-tracker.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Graduate school application tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Made by Jesus E. Vazquez for students applying to biostatistics and statistics programs. Copy it and make it yours.</t>
+    <t xml:space="preserve">Made by Jesus E. Vazquez with help from Claude, an AI assistant, for students applying to biostatistics and statistics programs. Please modify it to fit your needs. Add or rename columns freely; before deleting a column, check that no gray formula cell uses it.</t>
   </si>
   <si>
     <t xml:space="preserve">At a glance</t>
